--- a/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33385</t>
+          <t>33453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39058</t>
+          <t>39621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>67580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45174</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57959</t>
+          <t>58359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>48843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62917</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99520</t>
+          <t>99443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119255</t>
+          <t>118336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57932</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78368</t>
+          <t>77586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>52669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>73831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115154</t>
+          <t>116004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143556</t>
+          <t>143103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>109660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129314</t>
+          <t>130694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115690</t>
+          <t>114900</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136495</t>
+          <t>136062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232421</t>
+          <t>232874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260823</t>
+          <t>259973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>29235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44613</t>
+          <t>44232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64577</t>
+          <t>64583</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86058</t>
+          <t>86116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>42247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57368</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56291</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72149</t>
+          <t>71900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103682</t>
+          <t>103624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125163</t>
+          <t>125157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56885</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66312</t>
+          <t>65589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91152</t>
+          <t>91443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118390</t>
+          <t>117192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>93153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111706</t>
+          <t>111302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81782</t>
+          <t>82505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101922</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180779</t>
+          <t>181977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208017</t>
+          <t>207726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344083</t>
+          <t>343708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>397200</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308628</t>
+          <t>307455</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>342534</t>
+          <t>341925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>357717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>634708</t>
+          <t>642214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>687825</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46305</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>62229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84620</t>
+          <t>84441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57816</t>
+          <t>56691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>73422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68365</t>
+          <t>69856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85669</t>
+          <t>85613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131543</t>
+          <t>131722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154901</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>44529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64212</t>
+          <t>63495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>48217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69754</t>
+          <t>69008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98093</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128193</t>
+          <t>126664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95132</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114336</t>
+          <t>114815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123470</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145098</t>
+          <t>145007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224375</t>
+          <t>225904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254475</t>
+          <t>254728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26659</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>25336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78295</t>
+          <t>78447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55500</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>61441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>76476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121498</t>
+          <t>121346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145139</t>
+          <t>143392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45910</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47639</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>81400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106406</t>
+          <t>106790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69610</t>
+          <t>69576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>85874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65466</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84063</t>
+          <t>84874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140815</t>
+          <t>140431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165567</t>
+          <t>165821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>181319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>165504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>202389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>373546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>295646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>328387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>337877</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375104</t>
+          <t>373277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>645549</t>
+          <t>642200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693180</t>
+          <t>692702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41351</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60946</t>
+          <t>62308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69862</t>
+          <t>69623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84212</t>
+          <t>84206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>64880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79882</t>
+          <t>78917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140025</t>
+          <t>138663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159620</t>
+          <t>159294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,26%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36850</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>54033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61678</t>
+          <t>60750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84098</t>
+          <t>84284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104877</t>
+          <t>103675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133325</t>
+          <t>133752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>102232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119415</t>
+          <t>119954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126494</t>
+          <t>126308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>148914</t>
+          <t>149842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233532</t>
+          <t>233105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>261980</t>
+          <t>263182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44446</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63916</t>
+          <t>64249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37549</t>
+          <t>38079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56150</t>
+          <t>55671</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87739</t>
+          <t>88590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114810</t>
+          <t>113705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80398</t>
+          <t>80065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>76500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94622</t>
+          <t>94092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161675</t>
+          <t>162780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188746</t>
+          <t>187895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37547</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35764</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54576</t>
+          <t>55007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77689</t>
+          <t>78137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103392</t>
+          <t>103813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66064</t>
+          <t>66201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84559</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>74997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94240</t>
+          <t>93896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148718</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174421</t>
+          <t>173973</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189092</t>
+          <t>189234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171826</t>
+          <t>171223</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209631</t>
+          <t>207722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333531</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>382916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336298</t>
+          <t>336156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372652</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361402</t>
+          <t>363311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>399810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709325</t>
+          <t>713507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762892</t>
+          <t>762091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55773</t>
+          <t>55527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96550</t>
+          <t>96547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107947</t>
+          <t>108064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123204</t>
+          <t>121559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140008</t>
+          <t>139216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>155217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169876</t>
+          <t>170198</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282893</t>
+          <t>282825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305800</t>
+          <t>305968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36053</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58960</t>
+          <t>59028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146526</t>
+          <t>145957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160606</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164332</t>
+          <t>164056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185200</t>
+          <t>185576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318545</t>
+          <t>317268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342699</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27290</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43679</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67833</t>
+          <t>69110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>215929</t>
+          <t>216897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246666</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252496</t>
+          <t>252613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274672</t>
+          <t>276247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474186</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514800</t>
+          <t>516612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59529</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52987</t>
+          <t>52870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66140</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106754</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>548406</t>
+          <t>549921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>588993</t>
+          <t>590002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>637741</t>
+          <t>637030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>673605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1198846</t>
+          <t>1200986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1254226</t>
+          <t>1252460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77162</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117749</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>124942</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173901</t>
+          <t>175667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229281</t>
+          <t>227141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32010</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25111</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39766</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26580</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20200</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33453</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19623</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33335</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32010</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24876</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>39621</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48687</t>
+          <t>49047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67580</t>
+          <t>69455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48698</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63353</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51979</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45106</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58359</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45224</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58936</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48843</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63588</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99443</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118336</t>
+          <t>117976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>62564</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53044</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73225</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>66416</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56552</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>77586</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56385</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77322</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>35,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62564</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>52669</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>73831</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116004</t>
+          <t>115653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143103</t>
+          <t>144983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>126167</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>115506</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>135687</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>120830</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>109660</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130694</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109924</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>130861</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>126167</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>114900</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>136062</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232874</t>
+          <t>230994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>259973</t>
+          <t>260324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38471</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30947</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46878</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>36565</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29235</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44232</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29145</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44766</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>42,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>38471</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>31361</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46491</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64583</t>
+          <t>63771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86116</t>
+          <t>86151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64790</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56383</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>72314</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>49914</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>42247</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57244</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41713</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57334</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>57,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64790</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56770</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>71900</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>62,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>103589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125157</t>
+          <t>125969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55639</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46556</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65467</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>48477</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39773</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57922</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39712</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57752</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>26,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>55639</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46289</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>65589</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91443</t>
+          <t>91013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117192</t>
+          <t>118108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92455</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82627</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>101538</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>102598</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>93153</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>111302</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>93323</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>111363</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>92455</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>82505</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>101805</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181977</t>
+          <t>181061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207726</t>
+          <t>208156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>172022</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>207056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>161434</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>195904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>160422</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>195426</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>170832</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207188</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343708</t>
+          <t>343940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389694</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>339866</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>321493</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>356527</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>325321</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>307455</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341925</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>307933</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>342937</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>339866</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>321361</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357717</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>642214</t>
+          <t>639866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688200</t>
+          <t>687968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34383</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26954</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42989</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38564</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30699</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47430</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30875</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47091</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34383</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26430</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42187</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62229</t>
+          <t>62755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84441</t>
+          <t>84302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77660</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>69054</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85089</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>65557</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56691</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73422</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57030</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73246</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>77660</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>69856</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85613</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131722</t>
+          <t>131861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153934</t>
+          <t>153408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58228</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48924</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70509</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>53984</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44529</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>63495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44959</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>63759</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>58228</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>48217</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>69008</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97840</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126664</t>
+          <t>126865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134996</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>122715</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>144300</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105360</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95849</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114815</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95585</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>114385</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>134996</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>124216</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>145007</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>69,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225904</t>
+          <t>225703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254728</t>
+          <t>255503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33037</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25582</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40559</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33645</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25648</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41196</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26012</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42459</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>33037</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25336</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40371</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78447</t>
+          <t>77528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68775</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61253</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76230</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64335</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56784</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72332</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55521</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71968</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68775</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61441</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76476</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>67,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121346</t>
+          <t>122265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143392</t>
+          <t>143616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56217</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47125</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65122</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37741</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29646</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>45944</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29831</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46341</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>56217</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46828</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>64806</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81400</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106790</t>
+          <t>106615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75485</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66580</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>84577</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77779</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69576</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85874</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>69179</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>85689</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>75485</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>66896</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>84874</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140431</t>
+          <t>140606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165821</t>
+          <t>165645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>162166</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>200479</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148578</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>181319</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>147102</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>181161</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>165504</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>202389</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>323044</t>
+          <t>322120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373546</t>
+          <t>370964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>356916</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>338302</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>376615</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>313031</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>295646</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>328387</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>295804</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>329863</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>356916</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>336392</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>373277</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>642200</t>
+          <t>644782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>692702</t>
+          <t>693626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25383</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18731</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32882</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25496</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18498</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33081</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19078</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33412</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25383</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19350</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33387</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41677</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62308</t>
+          <t>60916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72884</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65385</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77208</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69623</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>84206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>69292</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>83626</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72884</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64880</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78917</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138663</t>
+          <t>140055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159294</t>
+          <t>160232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102704</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60786</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83646</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>45539</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36311</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54033</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>37184</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54026</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>72289</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>60750</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84284</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103675</t>
+          <t>102028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133752</t>
+          <t>131038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>138303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>126946</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>149806</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>110726</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>102232</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119954</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102239</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119081</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>138303</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>126308</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>149842</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>233105</t>
+          <t>235819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263182</t>
+          <t>264829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>156265</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46510</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37732</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55879</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>53994</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44885</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64249</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45368</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>64759</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>46510</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>38079</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>55671</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88590</t>
+          <t>88435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113705</t>
+          <t>113845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85661</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76292</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94439</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>64,81%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>57,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90320</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80065</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99429</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79555</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>98946</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85661</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76500</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94092</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162780</t>
+          <t>162640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187895</t>
+          <t>188050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144314</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44751</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35219</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55125</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45955</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36626</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55905</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37656</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55710</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>37,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44751</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36108</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55007</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78137</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103813</t>
+          <t>103259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85253</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74879</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94785</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76151</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>66201</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>85480</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>66396</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>84450</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85253</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74997</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>93896</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>148851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>173973</t>
+          <t>173454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>170425</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208535</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>152883</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188892</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>171223</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207722</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>334332</t>
+          <t>333384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>382916</t>
+          <t>386607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>382101</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>362498</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>400608</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,16%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>354405</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>336156</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>370871</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>336498</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>372507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,46%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>382101</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>363311</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>399810</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>713507</t>
+          <t>709816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762091</t>
+          <t>763039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41979</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37662</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45094</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51300</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47192</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>54472</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55527</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>102849</t>
+          <t>88817</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96547</t>
+          <t>83577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108064</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8558</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12875</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3039</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10319</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>140632</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>132337</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>146197</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>84,01%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>131973</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>121559</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>139216</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>163488</t>
+          <t>122326</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155217</t>
+          <t>114148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170198</t>
+          <t>128631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>295461</t>
+          <t>262958</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282825</t>
+          <t>252336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305968</t>
+          <t>271371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16890</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25185</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27326</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37740</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>46392</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35885</t>
+          <t>31668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59028</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>164763</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>154537</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>173510</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>154935</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>145957</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>161008</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>176172</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164056</t>
+          <t>146841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185576</t>
+          <t>161885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>331107</t>
+          <t>320048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317268</t>
+          <t>306351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>332073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35363</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26616</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45589</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18953</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12880</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27931</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48434</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>55596</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43654</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>69293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>254492</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>242496</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>264683</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>233358</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>216897</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>248020</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>90,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>265405</t>
+          <t>220501</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252613</t>
+          <t>209660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276247</t>
+          <t>229383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>498762</t>
+          <t>474993</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>476890</t>
+          <t>459147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>516612</t>
+          <t>488989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38153</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27962</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50149</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42100</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27438</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58561</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40078</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52870</t>
+          <t>46893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82178</t>
+          <t>74205</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64328</t>
+          <t>60209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104050</t>
+          <t>90051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>583378</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>616585</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>816</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>549921</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>590002</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544949</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>637030</t>
+          <t>529290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>673605</t>
+          <t>559406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146816</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1200986</t>
+          <t>1124354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1252460</t>
+          <t>1167240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98964</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84244</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117451</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>94590</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76153</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116234</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>84729</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>70272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>199946</t>
+          <t>183692</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175667</t>
+          <t>163268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227141</t>
+          <t>206154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
